--- a/out/global_metric/excel/resnet.xlsx
+++ b/out/global_metric/excel/resnet.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,15 +450,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -469,20 +489,32 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8988095238095237</v>
+        <v>0.863095223903656</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7269841182989419</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8452852802468728</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44</v>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>101</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -493,20 +525,32 @@
         <v>29</v>
       </c>
       <c r="B3" t="n">
-        <v>0.857142857142857</v>
+        <v>0.8809523582458496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7307256153853525</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8758681787324347</v>
+      </c>
+      <c r="D3" t="n">
+        <v>57</v>
       </c>
       <c r="E3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>91</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -517,20 +561,32 @@
         <v>48</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9166666666666669</v>
+        <v>0.9107142686843872</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7191609890343644</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9071310065064953</v>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
       </c>
       <c r="E4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>93</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -541,20 +597,32 @@
         <v>67</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.875</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7243764089342944</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.865338366589345</v>
+      </c>
+      <c r="D5" t="n">
+        <v>51</v>
       </c>
       <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13</v>
+      </c>
+      <c r="G5" t="n">
+        <v>96</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -565,140 +633,32 @@
         <v>86</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8511904761904762</v>
+        <v>0.8690476417541504</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6841269751560847</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.860317455210179</v>
+      </c>
+      <c r="D6" t="n">
+        <v>52</v>
       </c>
       <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="n">
+        <v>94</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>105</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8095238095238094</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5164399030663049</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>124</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.886904761904762</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7458049796756966</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>143</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6987528262019221</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>162</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8392857142857143</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.5950113305354848</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>181</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8452380952380952</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6055555482235452</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>101</t>
         </is>
@@ -715,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -736,15 +696,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -755,20 +735,32 @@
         <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8273809523809523</v>
+        <v>0.8452380895614624</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5801587228558202</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8274063486623069</v>
+      </c>
+      <c r="D2" t="n">
+        <v>44</v>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G2" t="n">
+        <v>98</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -779,20 +771,32 @@
         <v>30</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.863095223903656</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6918367266141886</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.850365947742356</v>
+      </c>
+      <c r="D3" t="n">
+        <v>48</v>
       </c>
       <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>97</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -803,20 +807,32 @@
         <v>49</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6246031672195769</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8990384564257236</v>
+      </c>
+      <c r="D4" t="n">
+        <v>56</v>
       </c>
       <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>96</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -827,20 +843,32 @@
         <v>68</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8452380895614624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6513605365129983</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8314814763900207</v>
+      </c>
+      <c r="D5" t="n">
+        <v>47</v>
       </c>
       <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17</v>
+      </c>
+      <c r="G5" t="n">
+        <v>95</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -851,140 +879,32 @@
         <v>87</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8511904761904761</v>
+        <v>0.875</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6769841182929895</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.865338366589345</v>
+      </c>
+      <c r="D6" t="n">
+        <v>51</v>
       </c>
       <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>96</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>106</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8511904761904759</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.5825396755436509</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>125</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8511904761904762</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.688888880210053</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>144</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8095238095238096</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.6092970450520194</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>163</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8095238095238098</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.5709750493480862</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>182</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8273809523809524</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6428571353472222</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>152</t>
         </is>
@@ -1001,7 +921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,15 +942,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -1041,20 +981,32 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9404761904761904</v>
+        <v>0.9226190447807312</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8031745936084657</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9198914228455006</v>
+      </c>
+      <c r="D2" t="n">
+        <v>62</v>
       </c>
       <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>93</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1065,20 +1017,32 @@
         <v>31</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8988095238095237</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7204081551379981</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8990384564257236</v>
+      </c>
+      <c r="D3" t="n">
+        <v>56</v>
       </c>
       <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" t="n">
+        <v>96</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1089,20 +1053,32 @@
         <v>50</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8869047619047618</v>
+        <v>0.875</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6997732344250351</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8711609341859169</v>
+      </c>
+      <c r="D4" t="n">
+        <v>59</v>
       </c>
       <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>88</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1113,20 +1089,32 @@
         <v>69</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9107142857142858</v>
+        <v>0.9166666865348816</v>
       </c>
       <c r="C5" t="n">
-        <v>0.719047610904762</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9116586487317327</v>
+      </c>
+      <c r="D5" t="n">
+        <v>57</v>
       </c>
       <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>97</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1137,140 +1125,32 @@
         <v>88</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8928571428571428</v>
+        <v>0.9107142686843872</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7801587209847883</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9075670271459378</v>
+      </c>
+      <c r="D6" t="n">
+        <v>61</v>
       </c>
       <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>92</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>107</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8690476190476191</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6712018064170988</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>126</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8988095238095238</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7410430750506966</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>145</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8333333333333331</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7235827582544003</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>164</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9226190476190476</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7785714191388891</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>183</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7227891074356174</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1287,7 +1167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1308,15 +1188,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -1327,20 +1227,32 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9107142857142856</v>
+        <v>0.898809552192688</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7666666571646829</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8957017076554085</v>
+      </c>
+      <c r="D2" t="n">
+        <v>61</v>
       </c>
       <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1351,20 +1263,32 @@
         <v>32</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8571428571428573</v>
+        <v>0.8571428656578064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.663492055765873</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8536372825770167</v>
+      </c>
+      <c r="D3" t="n">
+        <v>59</v>
       </c>
       <c r="E3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>85</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1375,20 +1299,32 @@
         <v>51</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.875</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6495464779076099</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8643859260942892</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
       </c>
       <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>97</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1399,20 +1335,32 @@
         <v>70</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7090702868659434</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.900694541962565</v>
+      </c>
+      <c r="D5" t="n">
+        <v>59</v>
       </c>
       <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>93</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1423,140 +1371,32 @@
         <v>89</v>
       </c>
       <c r="B6" t="n">
-        <v>0.869047619047619</v>
+        <v>0.8452380895614624</v>
       </c>
       <c r="C6" t="n">
-        <v>0.748979582540776</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8314814763900207</v>
+      </c>
+      <c r="D6" t="n">
+        <v>47</v>
       </c>
       <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17</v>
+      </c>
+      <c r="G6" t="n">
+        <v>95</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>108</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8511904761904762</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6672335524819135</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>127</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.688095229984127</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>146</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8809523809523808</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7481859323577073</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>165</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.9107142857142856</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7158730072328041</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>184</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.8214285714285715</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.6688208539309876</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -1573,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1594,15 +1434,35 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>tn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fp</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>fn</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tp</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>fold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>submodel</t>
         </is>
@@ -1613,20 +1473,32 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9464285714285714</v>
+        <v>0.9047619104385376</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8198412599298943</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9024248533564616</v>
+      </c>
+      <c r="D2" t="n">
+        <v>63</v>
       </c>
       <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>89</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1637,20 +1509,32 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8809523582458496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7501133702526187</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8784722171639903</v>
+      </c>
+      <c r="D3" t="n">
+        <v>62</v>
       </c>
       <c r="E3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>86</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1661,20 +1545,32 @@
         <v>52</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9226190476190476</v>
+        <v>0.9226190447807312</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7382086079311899</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9182114318024264</v>
+      </c>
+      <c r="D4" t="n">
+        <v>58</v>
       </c>
       <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>97</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1685,20 +1581,32 @@
         <v>71</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9285714285714284</v>
+        <v>0.9107142686843872</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6965986316062521</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.9038131175287492</v>
+      </c>
+      <c r="D5" t="n">
+        <v>54</v>
       </c>
       <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>99</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>50</t>
         </is>
@@ -1709,140 +1617,32 @@
         <v>90</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9047619047619044</v>
+        <v>0.8928571343421936</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7992063396236774</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
+        <v>0.8888235243151178</v>
+      </c>
+      <c r="D6" t="n">
+        <v>59</v>
       </c>
       <c r="E6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>91</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>109</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6945578151401848</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>128</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8928571428571428</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.7791383128211992</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>147</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8392857142857141</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.7180272027246384</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>166</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8988095238095238</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.7198412612870372</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>185</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.7269841184973547</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>resnet</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>9</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>50</t>
         </is>

--- a/out/global_metric/excel/resnet.xlsx
+++ b/out/global_metric/excel/resnet.xlsx
@@ -499,25 +499,29 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.898809552192688</v>
+        <v>0.6553480625152588</v>
       </c>
       <c r="C2" t="n">
-        <v>0.888537636875536</v>
+        <v>0.6552844493789706</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>101</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7032514700795572</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7333242936493021</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -537,25 +541,29 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8333333134651184</v>
+        <v>0.7113752365112305</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8304253734749847</v>
+        <v>0.7111345699764834</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>218</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>81</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7587743572005072</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7617282073563295</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -575,25 +583,29 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>0.863095223903656</v>
+        <v>0.7028862237930298</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8561161743780112</v>
+        <v>0.696717809513087</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8053384065490604</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7960916071935111</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -613,25 +625,29 @@
         <v>79</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8690476417541504</v>
+        <v>0.6672325730323792</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8611778795076956</v>
+        <v>0.6663082387198238</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>212</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6864291479303585</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7287499569649118</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -651,25 +667,29 @@
         <v>102</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8273809552192688</v>
+        <v>0.706281840801239</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8049249198925672</v>
+        <v>0.7029908688039777</v>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>177</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G6" t="n">
-        <v>98</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8007033321803296</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7927971388720308</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -765,25 +785,29 @@
         <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8690476417541504</v>
+        <v>0.6977928876876831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.856320940333646</v>
+        <v>0.6975409029169496</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>214</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7788193243399055</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7836439735383435</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -803,25 +827,29 @@
         <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>0.886904776096344</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8804628642307554</v>
+        <v>0.7234837896875124</v>
       </c>
       <c r="D3" t="n">
-        <v>55</v>
+        <v>192</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8042372881355933</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7952569629648755</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -841,25 +869,29 @@
         <v>57</v>
       </c>
       <c r="B4" t="n">
-        <v>0.875</v>
+        <v>0.7368420958518982</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8623111996939508</v>
+        <v>0.7366933398472695</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>224</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8304277643260696</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8343334180919542</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -879,25 +911,29 @@
         <v>80</v>
       </c>
       <c r="B5" t="n">
-        <v>0.851190447807312</v>
+        <v>0.7215619683265686</v>
       </c>
       <c r="C5" t="n">
-        <v>0.84075828873503</v>
+        <v>0.7202062283437894</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>192</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>233</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8057304277643261</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8013278001534694</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -917,25 +953,29 @@
         <v>103</v>
       </c>
       <c r="B6" t="n">
-        <v>0.863095223903656</v>
+        <v>0.7300509214401245</v>
       </c>
       <c r="C6" t="n">
-        <v>0.84666057671378</v>
+        <v>0.7289226150270789</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>196</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F6" t="n">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>234</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8068257811599215</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8019513783848818</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1031,25 +1071,29 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9047619104385376</v>
+        <v>0.6757215857505798</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9024248533564616</v>
+        <v>0.6606825571712156</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>261</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7743802605788078</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7584253287430396</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1069,25 +1113,29 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>0.898809552192688</v>
+        <v>0.6977928876876831</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8909882005489479</v>
+        <v>0.6910523537029646</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7996829240170643</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7945897278293023</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1107,25 +1155,29 @@
         <v>58</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8690476417541504</v>
+        <v>0.7147707939147949</v>
       </c>
       <c r="C4" t="n">
-        <v>0.860317455210179</v>
+        <v>0.712074298431125</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8154156577885391</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8220002456116847</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1145,25 +1197,29 @@
         <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9107142686843872</v>
+        <v>0.6943972706794739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9079720943901542</v>
+        <v>0.6931865486833237</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>186</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="G5" t="n">
-        <v>91</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7788885045543641</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7705287707800972</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1183,25 +1239,29 @@
         <v>104</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9226190447807312</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9182114318024264</v>
+        <v>0.7064148881280445</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>187</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>97</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7871209500749452</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7794347934920116</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1297,25 +1357,29 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>0.875</v>
+        <v>0.6808149218559265</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8633776040159322</v>
+        <v>0.680740394009578</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>205</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="G2" t="n">
-        <v>98</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7673930589184828</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7791846040163899</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1335,25 +1399,29 @@
         <v>36</v>
       </c>
       <c r="B3" t="n">
-        <v>0.851190447807312</v>
+        <v>0.6926994919776917</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8427142966590845</v>
+        <v>0.6926675937491122</v>
       </c>
       <c r="D3" t="n">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="E3" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7720108382335985</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.7673597765776272</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1373,25 +1441,29 @@
         <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8809523582458496</v>
+        <v>0.7300509214401245</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8683385529152565</v>
+        <v>0.7294394943763696</v>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>201</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8168107921134555</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8199978666034833</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1411,25 +1483,29 @@
         <v>82</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.6876060962677002</v>
       </c>
       <c r="C5" t="n">
-        <v>0.91310772357763</v>
+        <v>0.6876052065528653</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>203</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>202</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7714401014643145</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7470689987484762</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1449,25 +1525,29 @@
         <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>0.8928571343421936</v>
+        <v>0.7045840620994568</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8815046971139838</v>
+        <v>0.7031456328190239</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
+        <v>187</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7778046811945117</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7670283066583519</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1563,25 +1643,29 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9464285969734192</v>
+        <v>0.7266553640365601</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9439979207369784</v>
+        <v>0.7260362176376149</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>200</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
-        <v>97</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8010146431453938</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7952775160032205</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1601,25 +1685,29 @@
         <v>37</v>
       </c>
       <c r="B3" t="n">
-        <v>0.898809552192688</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8947484747225708</v>
+        <v>0.7228798741943477</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>188</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8072696875360313</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.803244393962055</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1639,25 +1727,29 @@
         <v>60</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9166666865348816</v>
+        <v>0.7691001892089844</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9099126653376194</v>
+        <v>0.7690675472707538</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>223</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8395364925631269</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.838708499917562</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1677,25 +1769,29 @@
         <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.7266553640365601</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9299336441731624</v>
+        <v>0.7265418359872864</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8063761097659403</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7815841898309832</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>resnet</t>
@@ -1715,25 +1811,29 @@
         <v>106</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9047619104385376</v>
+        <v>0.7079796195030212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.900694541962565</v>
+        <v>0.7017686352853123</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>129</v>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8037818517237405</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.7877560179572202</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>resnet</t>

--- a/out/global_metric/excel/resnet.xlsx
+++ b/out/global_metric/excel/resnet.xlsx
@@ -499,28 +499,28 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6553480625152588</v>
+        <v>0.6893039345741272</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6552844493789706</v>
+        <v>0.689300317532263</v>
       </c>
       <c r="D2" t="n">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7032514700795572</v>
+        <v>0.7584572812175716</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7333242936493021</v>
+        <v>0.7558835687990468</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -541,28 +541,28 @@
         <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7113752365112305</v>
+        <v>0.7317487001419067</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7111345699764834</v>
+        <v>0.7317479483938661</v>
       </c>
       <c r="D3" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G3" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7587743572005072</v>
+        <v>0.7991756024443676</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7617282073563295</v>
+        <v>0.800929348907046</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -583,28 +583,28 @@
         <v>56</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7028862237930298</v>
+        <v>0.7521222233772278</v>
       </c>
       <c r="C4" t="n">
-        <v>0.696717809513087</v>
+        <v>0.7519155711521371</v>
       </c>
       <c r="D4" t="n">
-        <v>165</v>
+        <v>230</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="F4" t="n">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8053384065490604</v>
+        <v>0.8098005303816442</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7960916071935111</v>
+        <v>0.8249780748691943</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -625,28 +625,28 @@
         <v>79</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6672325730323792</v>
+        <v>0.7504244446754456</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6663082387198238</v>
+        <v>0.7497752976434965</v>
       </c>
       <c r="D5" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G5" t="n">
-        <v>181</v>
+        <v>236</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6864291479303585</v>
+        <v>0.8053038164418309</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7287499569649118</v>
+        <v>0.808639058319887</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -667,28 +667,28 @@
         <v>102</v>
       </c>
       <c r="B6" t="n">
-        <v>0.706281840801239</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7029908688039777</v>
+        <v>0.7199189806309474</v>
       </c>
       <c r="D6" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G6" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8007033321803296</v>
+        <v>0.8157557938429609</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7927971388720308</v>
+        <v>0.7793742377106819</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -785,28 +785,28 @@
         <v>11</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6977928876876831</v>
+        <v>0.7334465384483337</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6975409029169496</v>
+        <v>0.7333973316308489</v>
       </c>
       <c r="D2" t="n">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="E2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7788193243399055</v>
+        <v>0.8208693646950306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7836439735383435</v>
+        <v>0.8293114585487645</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -827,28 +827,28 @@
         <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7249575257301331</v>
+        <v>0.755517840385437</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7234837896875124</v>
+        <v>0.7553139879157924</v>
       </c>
       <c r="D3" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8042372881355933</v>
+        <v>0.8303643491294824</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7952569629648755</v>
+        <v>0.8292911273764885</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -869,28 +869,28 @@
         <v>57</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7368420958518982</v>
+        <v>0.7741935253143311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7366933398472695</v>
+        <v>0.7740658973483423</v>
       </c>
       <c r="D4" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8304277643260696</v>
+        <v>0.84369883546639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8343334180919542</v>
+        <v>0.84201067154306</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -911,28 +911,28 @@
         <v>80</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7215619683265686</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7202062283437894</v>
+        <v>0.7239829164049596</v>
       </c>
       <c r="D5" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G5" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8057304277643261</v>
+        <v>0.8104808024904878</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8013278001534694</v>
+        <v>0.7949007510921013</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -953,28 +953,28 @@
         <v>103</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7300509214401245</v>
+        <v>0.7691001892089844</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7289226150270789</v>
+        <v>0.768539061098807</v>
       </c>
       <c r="D6" t="n">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8068257811599215</v>
+        <v>0.8498212844459818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8019513783848818</v>
+        <v>0.8610938823267159</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1071,28 +1071,28 @@
         <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6757215857505798</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6606825571712156</v>
+        <v>0.7249567573413468</v>
       </c>
       <c r="D2" t="n">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="F2" t="n">
-        <v>157</v>
+        <v>81</v>
       </c>
       <c r="G2" t="n">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7743802605788078</v>
+        <v>0.8003459010722934</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7584253287430396</v>
+        <v>0.7865130038120434</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1113,28 +1113,28 @@
         <v>35</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6977928876876831</v>
+        <v>0.7181664109230042</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6910523537029646</v>
+        <v>0.7179314035057591</v>
       </c>
       <c r="D3" t="n">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7996829240170643</v>
+        <v>0.8166551366309236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7945897278293023</v>
+        <v>0.8028437557384701</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1155,28 +1155,28 @@
         <v>58</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7147707939147949</v>
+        <v>0.7589133977890015</v>
       </c>
       <c r="C4" t="n">
-        <v>0.712074298431125</v>
+        <v>0.7579582762380184</v>
       </c>
       <c r="D4" t="n">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8154156577885391</v>
+        <v>0.8450709097198201</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8220002456116847</v>
+        <v>0.8396638925787873</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1197,28 +1197,28 @@
         <v>81</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6943972706794739</v>
+        <v>0.7317487001419067</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6931865486833237</v>
+        <v>0.7315746309711845</v>
       </c>
       <c r="D5" t="n">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="G5" t="n">
         <v>223</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7788885045543641</v>
+        <v>0.8139974633921365</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7705287707800972</v>
+        <v>0.7970322927499561</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1239,28 +1239,28 @@
         <v>104</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7079796195030212</v>
+        <v>0.7453310489654541</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7064148881280445</v>
+        <v>0.7442096070420292</v>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7871209500749452</v>
+        <v>0.8339213651562321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7794347934920116</v>
+        <v>0.8364251636662818</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1357,28 +1357,28 @@
         <v>13</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6808149218559265</v>
+        <v>0.7198641896247864</v>
       </c>
       <c r="C2" t="n">
-        <v>0.680740394009578</v>
+        <v>0.7191355387842329</v>
       </c>
       <c r="D2" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="G2" t="n">
-        <v>196</v>
+        <v>227</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7673930589184828</v>
+        <v>0.8013951343249165</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7791846040163899</v>
+        <v>0.8040354793907403</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1399,28 +1399,28 @@
         <v>36</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6926994919776917</v>
+        <v>0.7572156190872192</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6926675937491122</v>
+        <v>0.7570363268829732</v>
       </c>
       <c r="D3" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7720108382335985</v>
+        <v>0.8346765824974057</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7673597765776272</v>
+        <v>0.8100813133136893</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1441,28 +1441,28 @@
         <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7300509214401245</v>
+        <v>0.7402377128601074</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7294394943763696</v>
+        <v>0.7383521860786617</v>
       </c>
       <c r="D4" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G4" t="n">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8168107921134555</v>
+        <v>0.8254237288135593</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8199978666034833</v>
+        <v>0.8168238225540323</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1483,28 +1483,28 @@
         <v>82</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6876060962677002</v>
+        <v>0.7130730152130127</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6876052065528653</v>
+        <v>0.7124231106890967</v>
       </c>
       <c r="D5" t="n">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7714401014643145</v>
+        <v>0.7958030669895078</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7470689987484762</v>
+        <v>0.7953089853185974</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1525,28 +1525,28 @@
         <v>105</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7045840620994568</v>
+        <v>0.7674023509025574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7031456328190239</v>
+        <v>0.7672306066628178</v>
       </c>
       <c r="D6" t="n">
-        <v>187</v>
+        <v>234</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="G6" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7778046811945117</v>
+        <v>0.8432837541796377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7670283066583519</v>
+        <v>0.8466939119269559</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1643,28 +1643,28 @@
         <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7266553640365601</v>
+        <v>0.7385398745536804</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7260362176376149</v>
+        <v>0.7380680061658909</v>
       </c>
       <c r="D2" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8010146431453938</v>
+        <v>0.8084745762711865</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7952775160032205</v>
+        <v>0.8076056852219275</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1685,28 +1685,28 @@
         <v>37</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7249575257301331</v>
+        <v>0.7487266659736633</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7228798741943477</v>
+        <v>0.7481975269897245</v>
       </c>
       <c r="D3" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F3" t="n">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8072696875360313</v>
+        <v>0.8374783811829818</v>
       </c>
       <c r="I3" t="n">
-        <v>0.803244393962055</v>
+        <v>0.8368923960522565</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         <v>60</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7691001892089844</v>
+        <v>0.7741935253143311</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7690675472707538</v>
+        <v>0.7738180088114963</v>
       </c>
       <c r="D4" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G4" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8395364925631269</v>
+        <v>0.8613167300818632</v>
       </c>
       <c r="I4" t="n">
-        <v>0.838708499917562</v>
+        <v>0.8530681112510194</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1769,28 +1769,28 @@
         <v>83</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7266553640365601</v>
+        <v>0.7623090147972107</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7265418359872864</v>
+        <v>0.762006460000731</v>
       </c>
       <c r="D5" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G5" t="n">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8063761097659403</v>
+        <v>0.8197970713709213</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7815841898309832</v>
+        <v>0.8029424609232831</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -1811,28 +1811,28 @@
         <v>106</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7079796195030212</v>
+        <v>0.784380316734314</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7017686352853123</v>
+        <v>0.7843778144518143</v>
       </c>
       <c r="D6" t="n">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8037818517237405</v>
+        <v>0.8600945462930936</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7877560179572202</v>
+        <v>0.8642484639184342</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
